--- a/Result/04-01-25/NASDAQstock_04-01-25period252RS90.xlsx
+++ b/Result/04-01-25/NASDAQstock_04-01-25period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/04-01-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CA887A-C339-8A47-8D31-CA509CE182A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABF1FE4-E769-414D-B396-5B78F696AB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3310,7 +3310,7 @@
       </c>
     </row>
     <row r="20" spans="1:40">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B20">

--- a/Result/04-01-25/NASDAQstock_04-01-25period252RS90.xlsx
+++ b/Result/04-01-25/NASDAQstock_04-01-25period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/04-01-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABF1FE4-E769-414D-B396-5B78F696AB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7AA967-4A77-4A40-9CF5-A1375DBA5D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
